--- a/09_submission/05_supplementary/Supplementary_Tables.xlsx
+++ b/09_submission/05_supplementary/Supplementary_Tables.xlsx
@@ -469,7 +469,7 @@
   <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="92" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
     <col width="44" customWidth="1" min="4" max="4"/>
@@ -521,7 +521,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Table S1</t>
+          <t>Supplementary Table 1</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -541,7 +541,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Table S2</t>
+          <t>Supplementary Table 2</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -561,7 +561,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Table S3</t>
+          <t>Supplementary Table 3</t>
         </is>
       </c>
       <c r="B8" s="4" t="inlineStr">
@@ -581,7 +581,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Table S4</t>
+          <t>Supplementary Table 4</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
@@ -601,7 +601,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Table S5</t>
+          <t>Supplementary Table 5</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
@@ -621,7 +621,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Table S6</t>
+          <t>Supplementary Table 6</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -641,7 +641,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Table S7</t>
+          <t>Supplementary Table 7</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -661,7 +661,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Table S8</t>
+          <t>Supplementary Table 8</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -681,7 +681,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Table S9</t>
+          <t>Supplementary Table 9</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Table S10</t>
+          <t>Supplementary Table 10</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Table S11</t>
+          <t>Supplementary Table 11</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -741,7 +741,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Table S12</t>
+          <t>Supplementary Table 12</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -761,7 +761,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Table S13</t>
+          <t>Supplementary Table 13</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Table S14</t>
+          <t>Supplementary Table 14</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
@@ -801,7 +801,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Table S15</t>
+          <t>Supplementary Table 15</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
@@ -821,7 +821,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Table S16</t>
+          <t>Supplementary Table 16</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
@@ -841,7 +841,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Table S17</t>
+          <t>Supplementary Table 17</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Table S18</t>
+          <t>Supplementary Table 18</t>
         </is>
       </c>
       <c r="B23" s="4" t="inlineStr">
@@ -881,7 +881,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Table S19</t>
+          <t>Supplementary Table 19</t>
         </is>
       </c>
       <c r="B24" s="4" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Table S20</t>
+          <t>Supplementary Table 20</t>
         </is>
       </c>
       <c r="B25" s="4" t="inlineStr">
@@ -921,7 +921,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Table S21</t>
+          <t>Supplementary Table 21</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Table S22</t>
+          <t>Supplementary Table 22</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
@@ -961,7 +961,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Table S23</t>
+          <t>Supplementary Table 23</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
@@ -981,7 +981,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Table S24</t>
+          <t>Supplementary Table 24</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Table S25</t>
+          <t>Supplementary Table 25</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -1021,7 +1021,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Table S26</t>
+          <t>Supplementary Table 26</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1041,7 +1041,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Table S27</t>
+          <t>Supplementary Table 27</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -1061,7 +1061,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Table S28</t>
+          <t>Supplementary Table 28</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
